--- a/Pesquisa_Operacional_21_10_2026.xlsx
+++ b/Pesquisa_Operacional_21_10_2026.xlsx
@@ -8,143 +8,211 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Fatec\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43580B85-E7D4-433E-A348-07A57ABF7240}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABA7F7C-3D57-4702-ADBE-C655C19A67BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="3" xr2:uid="{8D6C0FA3-C012-4463-B83B-7B6D56B3562A}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{8D6C0FA3-C012-4463-B83B-7B6D56B3562A}"/>
   </bookViews>
   <sheets>
     <sheet name="EX1" sheetId="3" r:id="rId1"/>
     <sheet name="EX2" sheetId="1" r:id="rId2"/>
     <sheet name="EX3" sheetId="4" r:id="rId3"/>
     <sheet name="EX4" sheetId="5" r:id="rId4"/>
+    <sheet name="Anotações" sheetId="6" r:id="rId5"/>
+    <sheet name="EX5" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="solver_adj" localSheetId="4" hidden="1">Anotações!#REF!</definedName>
     <definedName name="solver_adj" localSheetId="0" hidden="1">'EX1'!$B$3:$G$3</definedName>
     <definedName name="solver_adj" localSheetId="1" hidden="1">'EX2'!$B$5:$J$5</definedName>
     <definedName name="solver_adj" localSheetId="2" hidden="1">'EX3'!$B$5:$D$9</definedName>
     <definedName name="solver_adj" localSheetId="3" hidden="1">'EX4'!$B$5:$M$5</definedName>
+    <definedName name="solver_adj" localSheetId="5" hidden="1">'EX5'!$B$5:$K$5</definedName>
+    <definedName name="solver_cvg" localSheetId="4" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="1" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="2" hidden="1">0.0001</definedName>
     <definedName name="solver_cvg" localSheetId="3" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_drv" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_eng" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_est" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_est" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_itr" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="4" hidden="1">Anotações!#REF!</definedName>
     <definedName name="solver_lhs1" localSheetId="0" hidden="1">'EX1'!$I$7:$I$11</definedName>
     <definedName name="solver_lhs1" localSheetId="1" hidden="1">'EX2'!$L$9:$L$14</definedName>
     <definedName name="solver_lhs1" localSheetId="2" hidden="1">'EX3'!$F$27:$F$31</definedName>
     <definedName name="solver_lhs1" localSheetId="3" hidden="1">'EX4'!$O$12:$O$15</definedName>
+    <definedName name="solver_lhs1" localSheetId="5" hidden="1">'EX5'!$M$11:$M$15</definedName>
+    <definedName name="solver_lhs2" localSheetId="4" hidden="1">Anotações!#REF!</definedName>
     <definedName name="solver_lhs2" localSheetId="2" hidden="1">'EX3'!$F$32:$F$34</definedName>
     <definedName name="solver_lhs2" localSheetId="3" hidden="1">'EX4'!$O$9:$O$11</definedName>
+    <definedName name="solver_lhs2" localSheetId="5" hidden="1">'EX5'!$M$9:$M$10</definedName>
+    <definedName name="solver_mip" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_mip" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="4" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="1" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="2" hidden="1">30</definedName>
     <definedName name="solver_mni" localSheetId="3" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="4" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="1" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="2" hidden="1">0.075</definedName>
     <definedName name="solver_mrt" localSheetId="3" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_msl" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_nod" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_num" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_nwt" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="4" hidden="1">Anotações!#REF!</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">'EX1'!$J$4</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">'EX2'!$M$6</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">'EX3'!$G$24</definedName>
     <definedName name="solver_opt" localSheetId="3" hidden="1">'EX4'!$P$6</definedName>
+    <definedName name="solver_opt" localSheetId="5" hidden="1">'EX5'!$N$6</definedName>
+    <definedName name="solver_pre" localSheetId="4" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="3" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rbv" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rel1" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_rel1" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rel2" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_rel2" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rel2" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="4" hidden="1">Anotações!#REF!</definedName>
     <definedName name="solver_rhs1" localSheetId="0" hidden="1">'EX1'!$J$7:$J$11</definedName>
     <definedName name="solver_rhs1" localSheetId="1" hidden="1">'EX2'!$M$9:$M$14</definedName>
     <definedName name="solver_rhs1" localSheetId="2" hidden="1">'EX3'!$G$27:$G$31</definedName>
     <definedName name="solver_rhs1" localSheetId="3" hidden="1">'EX4'!$P$12:$P$15</definedName>
+    <definedName name="solver_rhs1" localSheetId="5" hidden="1">'EX5'!$N$11:$N$15</definedName>
+    <definedName name="solver_rhs2" localSheetId="4" hidden="1">Anotações!#REF!</definedName>
     <definedName name="solver_rhs2" localSheetId="2" hidden="1">'EX3'!$G$32:$G$34</definedName>
     <definedName name="solver_rhs2" localSheetId="3" hidden="1">'EX4'!$P$9:$P$11</definedName>
+    <definedName name="solver_rhs2" localSheetId="5" hidden="1">'EX5'!$N$9:$N$10</definedName>
+    <definedName name="solver_rlx" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_rlx" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_rsd" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="4" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="1" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_scl" localSheetId="3" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="4" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="1" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="2" hidden="1">100</definedName>
     <definedName name="solver_ssz" localSheetId="3" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="5" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="4" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="1" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="2" hidden="1">2147483647</definedName>
     <definedName name="solver_tim" localSheetId="3" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="4" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="1" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="2" hidden="1">0.01</definedName>
     <definedName name="solver_tol" localSheetId="3" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
+    <definedName name="solver_typ" localSheetId="4" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="1" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
     <definedName name="solver_typ" localSheetId="3" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_val" localSheetId="4" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="1" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
     <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_ver" localSheetId="4" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="1" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">3</definedName>
     <definedName name="solver_ver" localSheetId="3" hidden="1">3</definedName>
+    <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -155,8 +223,66 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Fatec</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{E1464EFF-3D4F-43B7-BB29-3D749DA32184}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Restrições de capacidade.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{60F0A538-ADB9-4FE2-A479-A3001CE2F80B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fatec:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Restrições de demanda.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
   <si>
     <t>X11</t>
   </si>
@@ -309,13 +435,96 @@
   </si>
   <si>
     <t>Usar menor ou igual para capacidades</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>ARA</t>
+  </si>
+  <si>
+    <t>SJC</t>
+  </si>
+  <si>
+    <t>CAMP</t>
+  </si>
+  <si>
+    <t>BM</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>BH</t>
+  </si>
+  <si>
+    <t>RJ</t>
+  </si>
+  <si>
+    <t>CAP1</t>
+  </si>
+  <si>
+    <t>CAP2</t>
+  </si>
+  <si>
+    <t>X35</t>
+  </si>
+  <si>
+    <t>X45</t>
+  </si>
+  <si>
+    <t>X36</t>
+  </si>
+  <si>
+    <t>X46</t>
+  </si>
+  <si>
+    <t>X37</t>
+  </si>
+  <si>
+    <t>X47</t>
+  </si>
+  <si>
+    <t>Transbordo: X13 + X23 - X35 - X36 - X37 = 0</t>
+  </si>
+  <si>
+    <t>Transbordo: X14 + X24 - X45 - X46 - X47 = 0</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>Transbordo1</t>
+  </si>
+  <si>
+    <t>Transbordo2</t>
+  </si>
+  <si>
+    <t>Custos</t>
+  </si>
+  <si>
+    <r>
+      <t>Cada conexão pode ser chamada de X</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t>ij</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,6 +536,25 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -386,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -399,6 +627,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,6 +886,827 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>468603</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>172897</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E507A8EA-FA79-4ADC-BDD6-EC33EF8B9C09}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11496675" y="314325"/>
+          <a:ext cx="5402553" cy="3116122"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>490803</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>93974</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagem 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{535AEC61-3CE9-487B-933F-2A24898CA188}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5891478" y="581025"/>
+          <a:ext cx="8442371" cy="2667000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>287025</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>105044</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE7BC57F-63D5-4BFC-86B5-36C276B35700}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="287025" y="3371849"/>
+          <a:ext cx="5608950" cy="5419995"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>666750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Retângulo 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18CE79BC-0D60-462E-AE5C-02BAD548024F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5905500" y="2028825"/>
+          <a:ext cx="5791200" cy="200025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9524</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>62085</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>11202</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>48688</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1E4D03F-8859-4DCE-BC06-25DA497B6C3E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11039474" y="243060"/>
+          <a:ext cx="6259603" cy="3968053"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>81084</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>41275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>87465</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>23166</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagem 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20B477DB-46AB-4B44-824A-888A0E68FA30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11172417" y="4179358"/>
+          <a:ext cx="5689631" cy="3040475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>74083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>582084</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>84667</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="Conector de Seta Reta 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C47C1E41-B336-455C-B396-E4EFFF3A48FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2423583" y="3312583"/>
+          <a:ext cx="518584" cy="10584"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>52917</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>116416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>582084</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>116416</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="Conector de Seta Reta 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA1EB2D2-126F-4281-AA05-BD0778CF02A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2413000" y="3534833"/>
+          <a:ext cx="529167" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>84667</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>84667</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>582084</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>84666</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="10" name="Conector de Seta Reta 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E020FD1-141A-4A9B-8FA7-D2F8B822DAEE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2444750" y="3323167"/>
+          <a:ext cx="497417" cy="179916"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>84667</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>105833</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>582084</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="Conector de Seta Reta 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{390CE4DA-D7EC-42E9-837A-A5053D72ADC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2444750" y="3344333"/>
+          <a:ext cx="497417" cy="201084"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>105833</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>105833</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="14" name="Conector de Seta Reta 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD5C95F5-8A00-42AF-A954-7523A016EA8D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3418417" y="3344333"/>
+          <a:ext cx="783166" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>497416</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>116417</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>592667</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>137583</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="Conector de Seta Reta 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F679748-4DD5-43DB-B9B5-A0C5B19AA03F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3471333" y="3354917"/>
+          <a:ext cx="709084" cy="201083"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>529166</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>560917</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="18" name="Conector de Seta Reta 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A855D5D-AFF3-45D5-98F6-2C8A6186852A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3503083" y="3333750"/>
+          <a:ext cx="645584" cy="423333"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>74083</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="20" name="Conector de Seta Reta 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66631AD5-1FA2-4D26-897D-33789652FA57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="3354917" y="3333750"/>
+          <a:ext cx="836083" cy="158750"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>349250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>74083</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>592667</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="22" name="Conector de Seta Reta 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC21A1E3-91D1-41F0-B47A-3792BA47CB07}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3323167" y="3492500"/>
+          <a:ext cx="857250" cy="52917"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>116416</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>455083</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="24" name="Conector de Seta Reta 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89E69900-C235-46FB-9708-F1E91133AE79}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3354917" y="3534833"/>
+          <a:ext cx="687916" cy="243417"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1727,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="3">
-        <f t="shared" ref="F28:F31" si="0">SUM(B7:D7)</f>
+        <f t="shared" ref="F29:F31" si="0">SUM(B7:D7)</f>
         <v>0</v>
       </c>
       <c r="G29" s="2">
@@ -2236,4 +3286,435 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55959255-9D28-406D-A17B-D91A8277EA8E}">
+  <dimension ref="A17"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3182269-5EEB-47EF-98DE-DB6658A6A93A}">
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="12" width="9.140625" style="1"/>
+    <col min="13" max="13" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B5" s="3">
+        <v>800</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>100</v>
+      </c>
+      <c r="E5" s="3">
+        <v>900</v>
+      </c>
+      <c r="F5" s="3">
+        <v>500</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>400</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>3</v>
+      </c>
+      <c r="J6" s="2">
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="3">
+        <f>SUMPRODUCT(B5:K5,B6:K6)</f>
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="M9" s="3">
+        <f>SUMPRODUCT($B$5:$C$5,B9:C9)</f>
+        <v>800</v>
+      </c>
+      <c r="N9" s="2">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="M10" s="3">
+        <f>SUMPRODUCT($D$5:$E$5,D10:E10)</f>
+        <v>1000</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="M11" s="3">
+        <f>SUMPRODUCT($F$5:$G$5,F11:G11)</f>
+        <v>500</v>
+      </c>
+      <c r="N11" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="M12" s="3">
+        <f>SUMPRODUCT($H$5:$I$5,H12:I12)</f>
+        <v>400</v>
+      </c>
+      <c r="N12" s="2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3">
+        <f>SUMPRODUCT($J$5:$K$5,J13:K13)</f>
+        <v>900</v>
+      </c>
+      <c r="N13" s="2">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="M14" s="3">
+        <f>B5+D5-F5-H5-J5</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2">
+        <v>1</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3">
+        <f>C5+E5-G5-I5-K5</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N17" s="7"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="1">
+        <v>800</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="G21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="M17:N18"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>